--- a/data/trans_orig/P36BPD09_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones de legumbres que consumen a la semana en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265423</t>
+          <t>266421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292539</t>
+          <t>292628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263384</t>
+          <t>263597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275719</t>
+          <t>276367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>536293</t>
+          <t>535200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563924</t>
+          <t>563513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>20763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>31524</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57857</t>
+          <t>59479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48978</t>
+          <t>49521</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92317</t>
+          <t>92652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47465</t>
+          <t>46949</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74703</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106587</t>
+          <t>103779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158146</t>
+          <t>158083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>276435</t>
+          <t>276200</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>336053</t>
+          <t>334608</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>285363</t>
+          <t>285168</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>324289</t>
+          <t>323403</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>575057</t>
+          <t>572352</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>644969</t>
+          <t>644959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116643</t>
+          <t>118783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169672</t>
+          <t>170889</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133910</t>
+          <t>134138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171317</t>
+          <t>169498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262018</t>
+          <t>263104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>325619</t>
+          <t>326524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18974</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>18315</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33273</t>
+          <t>33228</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158283</t>
+          <t>158678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194510</t>
+          <t>194015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177697</t>
+          <t>178591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208910</t>
+          <t>209918</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>348843</t>
+          <t>349003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392361</t>
+          <t>395538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109026</t>
+          <t>109036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144354</t>
+          <t>143626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123712</t>
+          <t>123624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155199</t>
+          <t>153168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>244027</t>
+          <t>242633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>286853</t>
+          <t>287482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>54159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47379</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47592</t>
+          <t>47789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89278</t>
+          <t>92102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137791</t>
+          <t>140057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183902</t>
+          <t>182943</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214260</t>
+          <t>214278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>347525</t>
+          <t>349029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368521</t>
+          <t>365988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>513493</t>
+          <t>511762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95673</t>
+          <t>95741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137468</t>
+          <t>139128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106630</t>
+          <t>108779</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>229475</t>
+          <t>231523</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>224123</t>
+          <t>224129</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>356079</t>
+          <t>359268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>117067</t>
+          <t>114994</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136759</t>
+          <t>137121</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136263</t>
+          <t>135780</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>154527</t>
+          <t>154582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>257845</t>
+          <t>257882</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>286044</t>
+          <t>286873</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33688</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>54450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51332</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69652</t>
+          <t>69742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89852</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117338</t>
+          <t>117091</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168152</t>
+          <t>166955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194961</t>
+          <t>194598</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>164061</t>
+          <t>163104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>187170</t>
+          <t>186885</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>339177</t>
+          <t>338930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>374053</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64951</t>
+          <t>64043</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91156</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61163</t>
+          <t>60849</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82673</t>
+          <t>83454</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131257</t>
+          <t>131771</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>165827</t>
+          <t>166567</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53961</t>
+          <t>53008</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23637</t>
+          <t>24287</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>78946</t>
+          <t>77663</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56039</t>
+          <t>56193</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>119036</t>
+          <t>116602</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>332395</t>
+          <t>332426</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>390495</t>
+          <t>389986</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>188224</t>
+          <t>185162</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>494562</t>
+          <t>494133</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>457818</t>
+          <t>420336</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>859146</t>
+          <t>859082</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>196669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>250215</t>
+          <t>248341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>282670</t>
+          <t>283566</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>634913</t>
+          <t>636565</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>504093</t>
+          <t>504124</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>947885</t>
+          <t>996217</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>27602</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>94629</t>
+          <t>95060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>56056</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>83549</t>
+          <t>85168</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>82545</t>
+          <t>80775</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>164715</t>
+          <t>168463</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>222822</t>
+          <t>211410</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>692331</t>
+          <t>694083</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>490256</t>
+          <t>487907</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>534808</t>
+          <t>532401</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>628742</t>
+          <t>640748</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1206823</t>
+          <t>1205125</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>148961</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>675209</t>
+          <t>688321</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>117919</t>
+          <t>120462</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>157301</t>
+          <t>158213</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>286444</t>
+          <t>285725</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>928258</t>
+          <t>920840</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,95%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>184945</t>
+          <t>179667</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>283277</t>
+          <t>276971</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>201327</t>
+          <t>199428</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>275251</t>
+          <t>277190</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>414824</t>
+          <t>417732</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>536823</t>
+          <t>537790</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4486,17 +4486,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2100565</t>
+          <t>2100566</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1641686</t>
+          <t>1627905</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2284010</t>
+          <t>2278571</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1828015</t>
+          <t>1812225</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2400044</t>
+          <t>2403435</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3776327</t>
+          <t>3717717</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4633761</t>
+          <t>4627011</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>916649</t>
+          <t>919853</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1649940</t>
+          <t>1629412</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>999172</t>
+          <t>997406</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1636689</t>
+          <t>1655952</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1968710</t>
+          <t>1974319</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2918186</t>
+          <t>2970747</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3454419</t>
+          <t>3454420</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD09_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD09_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>281561</t>
+          <t>283423</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266421</t>
+          <t>269204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292628</t>
+          <t>294151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>270615</t>
+          <t>295064</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263597</t>
+          <t>287040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276367</t>
+          <t>300679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>552175</t>
+          <t>578487</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535200</t>
+          <t>562819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563513</t>
+          <t>589706</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27926</t>
+          <t>29415</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>42095</t>
+          <t>44989</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59479</t>
+          <t>59530</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69084</t>
+          <t>69740</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49521</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92652</t>
+          <t>91973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>59329</t>
+          <t>61160</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46949</t>
+          <t>48547</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73136</t>
+          <t>75160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>128413</t>
+          <t>130900</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103779</t>
+          <t>107410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158083</t>
+          <t>157013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>307211</t>
+          <t>315511</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>276200</t>
+          <t>285311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>334608</t>
+          <t>342147</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>304364</t>
+          <t>326547</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>285168</t>
+          <t>304977</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323403</t>
+          <t>347524</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>611575</t>
+          <t>642057</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>572352</t>
+          <t>605146</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>644959</t>
+          <t>675823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>142095</t>
+          <t>145396</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118783</t>
+          <t>122774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170889</t>
+          <t>173158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>151276</t>
+          <t>158787</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134138</t>
+          <t>139423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169498</t>
+          <t>177853</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>293371</t>
+          <t>304183</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263104</t>
+          <t>273209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>326524</t>
+          <t>336618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20212</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>23552</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>176729</t>
+          <t>175260</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>158678</t>
+          <t>158579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194015</t>
+          <t>192287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>193258</t>
+          <t>192884</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178591</t>
+          <t>175732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209918</t>
+          <t>207073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>369986</t>
+          <t>368144</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>349003</t>
+          <t>346122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>395538</t>
+          <t>392615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>127207</t>
+          <t>128998</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109036</t>
+          <t>112455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143626</t>
+          <t>144357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138764</t>
+          <t>145810</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123624</t>
+          <t>131080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153168</t>
+          <t>163025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>265971</t>
+          <t>274808</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>242633</t>
+          <t>251605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287482</t>
+          <t>296438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>315172</t>
+          <t>315128</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>315172</t>
+          <t>315128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315172</t>
+          <t>315128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>344041</t>
+          <t>351376</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>344041</t>
+          <t>351376</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>344041</t>
+          <t>351376</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>659213</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>659213</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>659213</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>35446</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54159</t>
+          <t>56422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33471</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47838</t>
+          <t>49777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>73184</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47789</t>
+          <t>56986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92102</t>
+          <t>96009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>194555</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140057</t>
+          <t>169427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182943</t>
+          <t>220310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>267345</t>
+          <t>226626</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>214278</t>
+          <t>207552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349029</t>
+          <t>248043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>428464</t>
+          <t>421182</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365988</t>
+          <t>390360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>511762</t>
+          <t>454330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>57,25%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115819</t>
+          <t>141586</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95741</t>
+          <t>119233</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139128</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>174902</t>
+          <t>157597</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>108779</t>
+          <t>138518</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231523</t>
+          <t>175402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>290722</t>
+          <t>299183</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>224129</t>
+          <t>269644</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359268</t>
+          <t>330429</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>311193</t>
+          <t>371587</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>311193</t>
+          <t>371587</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>311193</t>
+          <t>371587</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>786911</t>
+          <t>793549</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>786911</t>
+          <t>793549</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>786911</t>
+          <t>793549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>19880</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>127545</t>
+          <t>149058</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114994</t>
+          <t>136738</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>137121</t>
+          <t>159598</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>145430</t>
+          <t>158595</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135780</t>
+          <t>148303</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>154582</t>
+          <t>168409</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>272975</t>
+          <t>307654</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>257882</t>
+          <t>292063</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>286873</t>
+          <t>323292</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,84%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>47126</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>36564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54450</t>
+          <t>58255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60212</t>
+          <t>64722</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51292</t>
+          <t>54813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69742</t>
+          <t>75168</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>102437</t>
+          <t>111849</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>96961</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117091</t>
+          <t>126453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>386513</t>
+          <t>431996</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>386513</t>
+          <t>431996</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>386513</t>
+          <t>431996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>9306</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>181256</t>
+          <t>180419</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>166955</t>
+          <t>166333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194598</t>
+          <t>193202</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>175851</t>
+          <t>178469</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163104</t>
+          <t>165659</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>186885</t>
+          <t>190402</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>357108</t>
+          <t>358888</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>338930</t>
+          <t>339504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>374053</t>
+          <t>377661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>77122</t>
+          <t>79853</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64043</t>
+          <t>66396</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>92381</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>71510</t>
+          <t>75014</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>64080</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83454</t>
+          <t>86098</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>148631</t>
+          <t>154867</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131771</t>
+          <t>136723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>166567</t>
+          <t>173447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>256122</t>
+          <t>262789</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>256122</t>
+          <t>262789</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>256122</t>
+          <t>262789</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>525758</t>
+          <t>533496</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>525758</t>
+          <t>533496</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>525758</t>
+          <t>533496</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26878</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53008</t>
+          <t>71278</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>54468</t>
+          <t>71296</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>56903</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77663</t>
+          <t>91149</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>92689</t>
+          <t>124280</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>102203</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>116602</t>
+          <t>151286</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>361026</t>
+          <t>406060</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>332426</t>
+          <t>375991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>389986</t>
+          <t>436155</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>367787</t>
+          <t>437191</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>185162</t>
+          <t>410501</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>494133</t>
+          <t>461560</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>728814</t>
+          <t>843251</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>420336</t>
+          <t>798611</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>859082</t>
+          <t>883212</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>59,31%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>223011</t>
+          <t>258617</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>196669</t>
+          <t>231643</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>248341</t>
+          <t>287789</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>426367</t>
+          <t>262880</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>283566</t>
+          <t>239028</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>636565</t>
+          <t>287529</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>649379</t>
+          <t>521497</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>504124</t>
+          <t>481499</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>996217</t>
+          <t>560525</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>622259</t>
+          <t>717661</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>622259</t>
+          <t>717661</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>622259</t>
+          <t>717661</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>848623</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1470882</t>
+          <t>1489027</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1470882</t>
+          <t>1489027</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1470882</t>
+          <t>1489027</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>64601</t>
+          <t>79244</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>61498</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>95060</t>
+          <t>99030</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>68664</t>
+          <t>79930</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>56056</t>
+          <t>64847</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85168</t>
+          <t>97414</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>133265</t>
+          <t>159173</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>80775</t>
+          <t>136504</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>168463</t>
+          <t>186349</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>504119</t>
+          <t>582114</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>211410</t>
+          <t>554556</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>694083</t>
+          <t>606410</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>513031</t>
+          <t>596575</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>487907</t>
+          <t>571951</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>532401</t>
+          <t>619932</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1017150</t>
+          <t>1178690</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>640748</t>
+          <t>1142680</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1205125</t>
+          <t>1214289</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>359368</t>
+          <t>136048</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>148961</t>
+          <t>117151</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>688321</t>
+          <t>161502</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>136036</t>
+          <t>154826</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>120462</t>
+          <t>135273</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>158213</t>
+          <t>176110</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>495404</t>
+          <t>290875</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>285725</t>
+          <t>261871</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>920840</t>
+          <t>325467</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928088</t>
+          <t>797406</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928088</t>
+          <t>797406</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928088</t>
+          <t>797406</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1645819</t>
+          <t>1628738</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1645819</t>
+          <t>1628738</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1645819</t>
+          <t>1628738</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>239080</t>
+          <t>273713</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>179667</t>
+          <t>233941</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>276971</t>
+          <t>310406</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>244195</t>
+          <t>281041</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>199428</t>
+          <t>251397</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>277190</t>
+          <t>313255</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>483276</t>
+          <t>554754</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>417732</t>
+          <t>502716</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>537790</t>
+          <t>603391</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2100566</t>
+          <t>2286401</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1627905</t>
+          <t>2222416</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2278571</t>
+          <t>2346394</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2237680</t>
+          <t>2411951</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1812225</t>
+          <t>2358902</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2403435</t>
+          <t>2463660</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4338246</t>
+          <t>4698353</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3717717</t>
+          <t>4616737</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4627011</t>
+          <t>4780572</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1114774</t>
+          <t>967040</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>919853</t>
+          <t>907373</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1629412</t>
+          <t>1031330</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1173237</t>
+          <t>1035210</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>997406</t>
+          <t>988178</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1655952</t>
+          <t>1083488</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2288011</t>
+          <t>2002250</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1974319</t>
+          <t>1929276</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2970747</t>
+          <t>2078546</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3454420</t>
+          <t>3527154</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3655112</t>
+          <t>3728202</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7109532</t>
+          <t>7255356</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
